--- a/product_selector_out/STM32G4x4.xlsx
+++ b/product_selector_out/STM32G4x4.xlsx
@@ -17402,7 +17402,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17490,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17754,7 +17754,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17908,7 +17908,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18568,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -19228,7 +19228,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -19316,7 +19316,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32G4x4.xlsx
+++ b/product_selector_out/STM32G4x4.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AM12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN12" s="4" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AM29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN29" s="4" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN31" s="4" t="inlineStr">
@@ -9637,9 +9637,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -9964,9 +9964,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -10291,9 +10291,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -10618,9 +10618,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -10945,9 +10945,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -11599,9 +11599,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -12253,9 +12253,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -12580,9 +12580,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -13234,9 +13234,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -13561,9 +13561,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN24" s="6" t="inlineStr">
@@ -13888,9 +13888,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -14542,9 +14542,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN27" s="6" t="inlineStr">
@@ -15196,9 +15196,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN29" s="6" t="inlineStr">
@@ -15523,9 +15523,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN30" s="6" t="inlineStr">
@@ -15850,9 +15850,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM31" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN31" s="6" t="inlineStr">
@@ -16177,9 +16177,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">
@@ -16504,9 +16504,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM33" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN33" s="6" t="inlineStr">
@@ -16831,9 +16831,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM34" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN34" s="6" t="inlineStr">

--- a/product_selector_out/STM32G4x4.xlsx
+++ b/product_selector_out/STM32G4x4.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM35"/>
+  <dimension ref="A1:BN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.984375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -8841,12 +8963,17 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -8867,16 +8994,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -8889,6 +9014,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -8908,7 +9034,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -8949,7 +9077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM35"/>
+  <dimension ref="A1:BN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9017,6 +9145,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9350,6 +9479,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -9445,6 +9579,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9767,7 +9902,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10094,7 +10234,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10421,7 +10566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10748,7 +10898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11075,7 +11230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11402,7 +11562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11729,7 +11894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12056,7 +12226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12383,7 +12558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12710,7 +12890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13037,7 +13222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13364,7 +13554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13691,7 +13886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14018,7 +14218,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14345,7 +14550,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14672,7 +14882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14999,7 +15214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15326,7 +15546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15653,7 +15878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15980,7 +16210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16307,7 +16542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16634,7 +16874,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16961,7 +17206,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17288,7 +17538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17296,8 +17551,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
